--- a/statistics_tables/variety_lodging_results.xlsx
+++ b/statistics_tables/variety_lodging_results.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t xml:space="preserve">location</t>
   </si>
@@ -33,6 +33,12 @@
   </si>
   <si>
     <t xml:space="preserve">groups</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p.value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LSD</t>
   </si>
   <si>
     <t xml:space="preserve">mean_group_se</t>
@@ -479,19 +485,25 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B2" t="n">
         <v>2022</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -500,33 +512,37 @@
         <v>0</v>
       </c>
       <c r="G2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" t="n">
+        <v>16</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.371355510461474</v>
+      </c>
+      <c r="I2"/>
+      <c r="J2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" t="n">
         <v>0.352825164504771</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>0.0339506172839506</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>10.3923048454133</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B3" t="n">
         <v>2022</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -535,33 +551,37 @@
         <v>0</v>
       </c>
       <c r="G3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" t="n">
+        <v>16</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.371355510461474</v>
+      </c>
+      <c r="I3"/>
+      <c r="J3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" t="n">
         <v>0.352825164504771</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>0.0339506172839506</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>10.3923048454133</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B4" t="n">
         <v>2022</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E4" t="n">
         <v>0.101851851851852</v>
@@ -570,33 +590,37 @@
         <v>0.101851851851852</v>
       </c>
       <c r="G4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I4" t="n">
+        <v>16</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.371355510461474</v>
+      </c>
+      <c r="I4"/>
+      <c r="J4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K4" t="n">
         <v>0.352825164504771</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>0.0339506172839506</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>10.3923048454133</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B5" t="n">
         <v>2023</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E5" t="n">
         <v>6.75925925925926</v>
@@ -605,33 +629,39 @@
         <v>0.0925925925925926</v>
       </c>
       <c r="G5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H5" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.0304247610268265</v>
       </c>
       <c r="I5" t="n">
+        <v>4.52940821974733</v>
+      </c>
+      <c r="J5" t="s">
+        <v>22</v>
+      </c>
+      <c r="K5" t="n">
         <v>9.92530078677001</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>9.25925925925926</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>1.07193248497116</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B6" t="n">
         <v>2023</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E6" t="n">
         <v>8.33333333333333</v>
@@ -640,33 +670,39 @@
         <v>1.48775128300081</v>
       </c>
       <c r="G6" t="s">
-        <v>21</v>
-      </c>
-      <c r="H6" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.0304247610268265</v>
       </c>
       <c r="I6" t="n">
+        <v>4.52940821974733</v>
+      </c>
+      <c r="J6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K6" t="n">
         <v>9.92530078677001</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>9.25925925925926</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>1.07193248497116</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B7" t="n">
         <v>2023</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E7" t="n">
         <v>12.6851851851852</v>
@@ -675,33 +711,39 @@
         <v>2.36754750894952</v>
       </c>
       <c r="G7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" t="s">
-        <v>23</v>
+        <v>16</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.0304247610268265</v>
       </c>
       <c r="I7" t="n">
+        <v>4.52940821974733</v>
+      </c>
+      <c r="J7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K7" t="n">
         <v>9.92530078677001</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>9.25925925925926</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>1.07193248497116</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B8" t="n">
         <v>2022</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -710,33 +752,37 @@
         <v>0</v>
       </c>
       <c r="G8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="e">
+        <v>16</v>
+      </c>
+      <c r="H8" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="I8"/>
+      <c r="J8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B9" t="n">
         <v>2022</v>
       </c>
       <c r="C9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -745,68 +791,76 @@
         <v>0</v>
       </c>
       <c r="G9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H9" t="s">
-        <v>15</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="e">
+        <v>16</v>
+      </c>
+      <c r="H9" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="I9"/>
+      <c r="J9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B10" t="n">
         <v>2022</v>
       </c>
       <c r="C10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="s">
+        <v>16</v>
+      </c>
+      <c r="H10" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="I10"/>
+      <c r="J10" t="s">
         <v>17</v>
       </c>
-      <c r="D10" t="s">
-        <v>13</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="s">
-        <v>14</v>
-      </c>
-      <c r="H10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="e">
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B11" t="n">
         <v>2023</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -815,33 +869,39 @@
         <v>0</v>
       </c>
       <c r="G11" t="s">
-        <v>19</v>
-      </c>
-      <c r="H11" t="s">
-        <v>25</v>
+        <v>21</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.00959121532772366</v>
       </c>
       <c r="I11" t="n">
+        <v>1.36521913383818</v>
+      </c>
+      <c r="J11" t="s">
+        <v>27</v>
+      </c>
+      <c r="K11" t="n">
         <v>3.02467958451426</v>
       </c>
-      <c r="J11" t="n">
+      <c r="L11" t="n">
         <v>0.709876543209877</v>
       </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
         <v>4.26085297992443</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B12" t="n">
         <v>2023</v>
       </c>
       <c r="C12" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E12" t="n">
         <v>1.94444444444444</v>
@@ -850,33 +910,39 @@
         <v>0.82268326842175</v>
       </c>
       <c r="G12" t="s">
-        <v>14</v>
-      </c>
-      <c r="H12" t="s">
-        <v>26</v>
+        <v>16</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.00959121532772366</v>
       </c>
       <c r="I12" t="n">
+        <v>1.36521913383818</v>
+      </c>
+      <c r="J12" t="s">
+        <v>28</v>
+      </c>
+      <c r="K12" t="n">
         <v>3.02467958451426</v>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>0.709876543209877</v>
       </c>
-      <c r="K12" t="n">
+      <c r="M12" t="n">
         <v>4.26085297992443</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B13" t="n">
         <v>2023</v>
       </c>
       <c r="C13" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E13" t="n">
         <v>0.185185185185185</v>
@@ -885,33 +951,39 @@
         <v>0.185185185185185</v>
       </c>
       <c r="G13" t="s">
-        <v>19</v>
-      </c>
-      <c r="H13" t="s">
-        <v>27</v>
+        <v>21</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.00959121532772366</v>
       </c>
       <c r="I13" t="n">
+        <v>1.36521913383818</v>
+      </c>
+      <c r="J13" t="s">
+        <v>29</v>
+      </c>
+      <c r="K13" t="n">
         <v>3.02467958451426</v>
       </c>
-      <c r="J13" t="n">
+      <c r="L13" t="n">
         <v>0.709876543209877</v>
       </c>
-      <c r="K13" t="n">
+      <c r="M13" t="n">
         <v>4.26085297992443</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B14" t="n">
         <v>2024</v>
       </c>
       <c r="C14" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D14" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E14" t="n">
         <v>0.0787037037037037</v>
@@ -920,33 +992,39 @@
         <v>0.0378466407330376</v>
       </c>
       <c r="G14" t="s">
-        <v>19</v>
-      </c>
-      <c r="H14" t="s">
-        <v>28</v>
+        <v>21</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.00000000000200533028487796</v>
       </c>
       <c r="I14" t="n">
+        <v>0.316635986656421</v>
+      </c>
+      <c r="J14" t="s">
+        <v>30</v>
+      </c>
+      <c r="K14" t="n">
         <v>0.867410715836552</v>
       </c>
-      <c r="J14" t="n">
+      <c r="L14" t="n">
         <v>0.486111111111111</v>
       </c>
-      <c r="K14" t="n">
+      <c r="M14" t="n">
         <v>1.78438775829233</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B15" t="n">
         <v>2024</v>
       </c>
       <c r="C15" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D15" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E15" t="n">
         <v>1.25925925925926</v>
@@ -955,33 +1033,39 @@
         <v>0.186214072969734</v>
       </c>
       <c r="G15" t="s">
-        <v>14</v>
-      </c>
-      <c r="H15" t="s">
-        <v>29</v>
+        <v>16</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.00000000000200533028487796</v>
       </c>
       <c r="I15" t="n">
+        <v>0.316635986656421</v>
+      </c>
+      <c r="J15" t="s">
+        <v>31</v>
+      </c>
+      <c r="K15" t="n">
         <v>0.867410715836552</v>
       </c>
-      <c r="J15" t="n">
+      <c r="L15" t="n">
         <v>0.486111111111111</v>
       </c>
-      <c r="K15" t="n">
+      <c r="M15" t="n">
         <v>1.78438775829233</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B16" t="n">
         <v>2024</v>
       </c>
       <c r="C16" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D16" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E16" t="n">
         <v>0.12037037037037</v>
@@ -990,33 +1074,39 @@
         <v>0.0462962962962963</v>
       </c>
       <c r="G16" t="s">
-        <v>19</v>
-      </c>
-      <c r="H16" t="s">
-        <v>30</v>
+        <v>21</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.00000000000200533028487796</v>
       </c>
       <c r="I16" t="n">
+        <v>0.316635986656421</v>
+      </c>
+      <c r="J16" t="s">
+        <v>32</v>
+      </c>
+      <c r="K16" t="n">
         <v>0.867410715836552</v>
       </c>
-      <c r="J16" t="n">
+      <c r="L16" t="n">
         <v>0.486111111111111</v>
       </c>
-      <c r="K16" t="n">
+      <c r="M16" t="n">
         <v>1.78438775829233</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B17" t="n">
         <v>2022</v>
       </c>
       <c r="C17" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D17" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E17" t="n">
         <v>0.37037037037037</v>
@@ -1025,33 +1115,37 @@
         <v>0.290282893636935</v>
       </c>
       <c r="G17" t="s">
-        <v>14</v>
-      </c>
-      <c r="H17" t="s">
-        <v>32</v>
-      </c>
-      <c r="I17" t="n">
+        <v>16</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.334488831003413</v>
+      </c>
+      <c r="I17"/>
+      <c r="J17" t="s">
+        <v>34</v>
+      </c>
+      <c r="K17" t="n">
         <v>2.49822058899998</v>
       </c>
-      <c r="J17" t="n">
+      <c r="L17" t="n">
         <v>0.709876543209877</v>
       </c>
-      <c r="K17" t="n">
+      <c r="M17" t="n">
         <v>3.51923248189563</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B18" t="n">
         <v>2022</v>
       </c>
       <c r="C18" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D18" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E18" t="n">
         <v>1.2037037037037</v>
@@ -1060,33 +1154,37 @@
         <v>0.565822243196175</v>
       </c>
       <c r="G18" t="s">
-        <v>14</v>
-      </c>
-      <c r="H18" t="s">
-        <v>33</v>
-      </c>
-      <c r="I18" t="n">
+        <v>16</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.334488831003413</v>
+      </c>
+      <c r="I18"/>
+      <c r="J18" t="s">
+        <v>35</v>
+      </c>
+      <c r="K18" t="n">
         <v>2.49822058899998</v>
       </c>
-      <c r="J18" t="n">
+      <c r="L18" t="n">
         <v>0.709876543209877</v>
       </c>
-      <c r="K18" t="n">
+      <c r="M18" t="n">
         <v>3.51923248189563</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B19" t="n">
         <v>2022</v>
       </c>
       <c r="C19" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D19" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E19" t="n">
         <v>0.555555555555556</v>
@@ -1095,33 +1193,37 @@
         <v>0.338583000122247</v>
       </c>
       <c r="G19" t="s">
-        <v>14</v>
-      </c>
-      <c r="H19" t="s">
-        <v>34</v>
-      </c>
-      <c r="I19" t="n">
+        <v>16</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.334488831003413</v>
+      </c>
+      <c r="I19"/>
+      <c r="J19" t="s">
+        <v>36</v>
+      </c>
+      <c r="K19" t="n">
         <v>2.49822058899998</v>
       </c>
-      <c r="J19" t="n">
+      <c r="L19" t="n">
         <v>0.709876543209877</v>
       </c>
-      <c r="K19" t="n">
+      <c r="M19" t="n">
         <v>3.51923248189563</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B20" t="n">
         <v>2023</v>
       </c>
       <c r="C20" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D20" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -1130,33 +1232,37 @@
         <v>0</v>
       </c>
       <c r="G20" t="s">
-        <v>14</v>
-      </c>
-      <c r="H20" t="s">
-        <v>15</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="e">
+        <v>16</v>
+      </c>
+      <c r="H20" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="I20"/>
+      <c r="J20" t="s">
+        <v>17</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B21" t="n">
         <v>2023</v>
       </c>
       <c r="C21" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D21" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -1165,68 +1271,76 @@
         <v>0</v>
       </c>
       <c r="G21" t="s">
-        <v>14</v>
-      </c>
-      <c r="H21" t="s">
-        <v>15</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="e">
+        <v>16</v>
+      </c>
+      <c r="H21" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="I21"/>
+      <c r="J21" t="s">
+        <v>17</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B22" t="n">
         <v>2023</v>
       </c>
       <c r="C22" t="s">
+        <v>19</v>
+      </c>
+      <c r="D22" t="s">
+        <v>15</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="s">
+        <v>16</v>
+      </c>
+      <c r="H22" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="I22"/>
+      <c r="J22" t="s">
         <v>17</v>
       </c>
-      <c r="D22" t="s">
-        <v>13</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="s">
-        <v>14</v>
-      </c>
-      <c r="H22" t="s">
-        <v>15</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="e">
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B23" t="n">
         <v>2024</v>
       </c>
       <c r="C23" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D23" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -1235,33 +1349,37 @@
         <v>0</v>
       </c>
       <c r="G23" t="s">
-        <v>14</v>
-      </c>
-      <c r="H23" t="s">
-        <v>15</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="e">
+        <v>16</v>
+      </c>
+      <c r="H23" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="I23"/>
+      <c r="J23" t="s">
+        <v>17</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B24" t="n">
         <v>2024</v>
       </c>
       <c r="C24" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D24" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -1270,53 +1388,61 @@
         <v>0</v>
       </c>
       <c r="G24" t="s">
-        <v>14</v>
-      </c>
-      <c r="H24" t="s">
-        <v>15</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="e">
+        <v>16</v>
+      </c>
+      <c r="H24" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="I24"/>
+      <c r="J24" t="s">
+        <v>17</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="e">
         <v>#NUM!</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B25" t="n">
         <v>2024</v>
       </c>
       <c r="C25" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" t="s">
+        <v>15</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="s">
+        <v>16</v>
+      </c>
+      <c r="H25" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="I25"/>
+      <c r="J25" t="s">
         <v>17</v>
       </c>
-      <c r="D25" t="s">
-        <v>13</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="s">
-        <v>14</v>
-      </c>
-      <c r="H25" t="s">
-        <v>15</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="e">
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="e">
         <v>#NUM!</v>
       </c>
     </row>
